--- a/assets/constructions/examples/ctd_mt4.xlsx
+++ b/assets/constructions/examples/ctd_mt4.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT6"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -659,11 +659,36 @@
           <t>thr_id</t>
         </is>
       </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TDC2L10090L320-I1.75ISOVTS</t>
+          <t>S2L06019L060-I48UNTMVTH</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -673,7 +698,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>TMDR - Drilling, Thread Milling &amp; Chamfering</t>
+          <t>MilliPro HD</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -684,34 +709,34 @@
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>M12</t>
+          <t>UNC 3-48-2xDo</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>M60</t>
+          <t>UN60</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>6H</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
+        <v>0.099</v>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="n">
+        <v>48</v>
+      </c>
+      <c r="N2" t="n">
+        <v>48</v>
+      </c>
+      <c r="O2" t="n">
+        <v>48</v>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Coarse</t>
@@ -727,32 +752,34 @@
         <v>4</v>
       </c>
       <c r="T2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U2" t="n">
-        <v>9</v>
+        <v>1.9</v>
       </c>
       <c r="V2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="n">
-        <v>32</v>
+        <v>1.588</v>
       </c>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="n">
-        <v>32</v>
+        <v>6.53</v>
       </c>
       <c r="AB2" t="n">
-        <v>80</v>
-      </c>
-      <c r="AC2" t="inlineStr"/>
+        <v>76</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>69.47</v>
+      </c>
       <c r="AD2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
@@ -762,7 +789,7 @@
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>VTS</t>
+          <t>VTH</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -778,7 +805,7 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>HA-10</t>
+          <t>HA-6</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
@@ -788,14 +815,10 @@
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>R262 (DIN 13)</t>
-        </is>
-      </c>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr"/>
       <c r="AR2" t="n">
@@ -803,15 +826,34 @@
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>2022 / Full MAIN VARDEX 2022-METRIC.pdf</t>
+          <t>2018/VARGUS2018-ENGweb.pdf</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>189.68</v>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AX2" t="n">
+        <v>17437.98</v>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TD-2L06050L178-I28UNFVTS</t>
+          <t>S2L10090L233-I14UNTMVTH</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -832,7 +874,7 @@
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNF 1/4"x28-2.5xDo  </t>
+          <t xml:space="preserve">UNC 7/16"x14-2xDo </t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -846,23 +888,23 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>0.25</v>
+        <v>0.438</v>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="N3" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="O3" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Fine</t>
+          <t>Coarse</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -872,33 +914,31 @@
       </c>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U3" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="V3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="n">
-        <v>2.721</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>4.58</v>
-      </c>
+        <v>5.443</v>
+      </c>
+      <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="n">
-        <v>17.8</v>
+        <v>25.11</v>
       </c>
       <c r="AB3" t="n">
-        <v>58</v>
+        <v>101</v>
       </c>
       <c r="AC3" t="n">
-        <v>40.2</v>
+        <v>75.89</v>
       </c>
       <c r="AD3" t="n">
         <v>0</v>
@@ -914,7 +954,7 @@
       <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>VTS</t>
+          <t>VTH</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -930,7 +970,7 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>HA-6</t>
+          <t>HA-10</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
@@ -955,11 +995,30 @@
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>271.23</v>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AX3" t="n">
+        <v>24935.18</v>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S2L06048L125-I1.0ISOTMVTH</t>
+          <t>S2L08066L245-I24UNTMVTH</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -980,37 +1039,37 @@
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>M6x1.0-2xDo</t>
+          <t xml:space="preserve">UNF 5/16"x24-3xDo </t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>M60</t>
+          <t>UN60</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>6H</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>6</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
+        <v>0.313</v>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="n">
+        <v>24</v>
+      </c>
+      <c r="N4" t="n">
+        <v>24</v>
+      </c>
+      <c r="O4" t="n">
+        <v>24</v>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Coarse</t>
+          <t>Fine</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -1026,25 +1085,25 @@
         <v>5</v>
       </c>
       <c r="U4" t="n">
-        <v>4.8</v>
+        <v>6.68</v>
       </c>
       <c r="V4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="n">
-        <v>1.2</v>
+        <v>3.175</v>
       </c>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="n">
-        <v>13.5</v>
+        <v>25.56</v>
       </c>
       <c r="AB4" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AC4" t="n">
-        <v>62.5</v>
+        <v>54.44</v>
       </c>
       <c r="AD4" t="n">
         <v>0</v>
@@ -1076,7 +1135,7 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>HA-6</t>
+          <t>HA-8</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
@@ -1101,11 +1160,30 @@
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>236.9</v>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AX4" t="n">
+        <v>21779.09</v>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TDC2L10090L260-I1.75ISOVTS</t>
+          <t>S2L10090L335-I14UNTMVTH</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1126,34 +1204,34 @@
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">M12x1.75-2xDo   </t>
+          <t xml:space="preserve">UNC 7/16"x14-3xDo </t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>M60</t>
+          <t>UN60</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>6H</t>
+          <t>2B</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>12</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
+        <v>0.438</v>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="n">
+        <v>14</v>
+      </c>
+      <c r="N5" t="n">
+        <v>14</v>
+      </c>
+      <c r="O5" t="n">
+        <v>14</v>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Coarse</t>
@@ -1166,10 +1244,10 @@
       </c>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U5" t="n">
         <v>9</v>
@@ -1179,26 +1257,24 @@
       </c>
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>8.35</v>
-      </c>
+        <v>5.443</v>
+      </c>
+      <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="n">
-        <v>26</v>
+        <v>35.31</v>
       </c>
       <c r="AB5" t="n">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="AC5" t="n">
-        <v>54</v>
+        <v>65.69</v>
       </c>
       <c r="AD5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
@@ -1208,7 +1284,7 @@
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>VTS</t>
+          <t>VTH</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
@@ -1249,11 +1325,30 @@
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>271.23</v>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AX5" t="n">
+        <v>24935.18</v>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TD-2L06048L180-I20UNCVTS</t>
+          <t>TDC2L08075L112-I27NPTVTS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1263,7 +1358,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MilliPro HD</t>
+          <t>TMDR - Drilling, Thread Milling &amp; Chamfering</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1274,33 +1369,33 @@
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">UNC 1/4"x20-2.5Do  </t>
+          <t>1/8" - 27 NPT</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>UN60</t>
+          <t>NPT60</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2B</t>
+          <t>Standard NPT</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.25</v>
+        <v>10.242</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="N6" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="O6" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -1314,39 +1409,35 @@
       </c>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U6" t="n">
-        <v>4.8</v>
+        <v>7.5</v>
       </c>
       <c r="V6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="n">
-        <v>3.81</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>4.29</v>
-      </c>
+        <v>11.2</v>
+      </c>
+      <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="n">
-        <v>18</v>
+        <v>11.2</v>
       </c>
       <c r="AB6" t="n">
-        <v>58</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>40</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
@@ -1372,7 +1463,7 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>HA-6</t>
+          <t>HA-8</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -1382,10 +1473,14 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>R</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr"/>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>USAS B2.1:1968</t>
+        </is>
+      </c>
       <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr"/>
       <c r="AR6" t="n">
@@ -1393,10 +1488,29 @@
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>2018/VARGUS2018-ENGweb.pdf</t>
+          <t>2022 / Full MAIN VARDEX 2022-METRIC.pdf</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>212.98</v>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="AX6" t="n">
+        <v>19580.04</v>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>PMKNSH</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
